--- a/geisbertlab/analysis/clinicaltables.xlsx
+++ b/geisbertlab/analysis/clinicaltables.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -15,7 +15,23 @@
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -251,7 +267,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -579,7 +595,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.140625" bestFit="1" customWidth="1"/>
@@ -588,7 +604,7 @@
     <col min="5" max="5" width="255.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -605,7 +621,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -622,7 +638,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -639,7 +655,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -656,7 +672,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -673,7 +689,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -690,7 +706,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -707,7 +723,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -724,7 +740,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -741,7 +757,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -758,7 +774,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -775,7 +791,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -792,7 +808,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -809,7 +825,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>43</v>
       </c>
@@ -826,7 +842,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>46</v>
       </c>
@@ -843,7 +859,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -860,7 +876,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>52</v>
       </c>
@@ -877,7 +893,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>55</v>
       </c>
@@ -894,7 +910,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>57</v>
       </c>
@@ -911,7 +927,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>60</v>
       </c>
@@ -928,7 +944,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>63</v>
       </c>
@@ -945,7 +961,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>65</v>
       </c>
@@ -962,7 +978,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>67</v>
       </c>
@@ -979,7 +995,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>70</v>
       </c>
@@ -996,7 +1012,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>72</v>
       </c>
